--- a/data/Earth.xlsx
+++ b/data/Earth.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LocaL_Data\TERCOM\Software\python\TERCOM_py\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Non-Admin\source\repos\Orbital Mechanics\SPS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C357FD-693B-4D2E-BC6A-45FDDAD6C31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746A647E-CBB3-4A16-9EB5-3FC8626C53D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{E459F509-91DB-4780-AC17-CE2B8D072DEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E459F509-91DB-4780-AC17-CE2B8D072DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -62,25 +63,19 @@
     <t>TAEPO</t>
   </si>
   <si>
-    <t>body_1</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>1e28</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
     <t>1.5e11</t>
+  </si>
+  <si>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>5.97e24</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -493,28 +488,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
